--- a/data/trans_orig/P20D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>75,97%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -2211,97 +2211,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -2667,97 +2667,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>828</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>358</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>445</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>335</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>911</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>859</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>44686</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>976</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>857</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>537</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>537</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2319,27 +2319,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>929</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>379</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>379</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>384</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>949</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>698</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>845</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>690</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>724</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
